--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79465</v>
+        <v>79467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135601328</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135588696</v>
       </c>
       <c r="B7" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135588701</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99211</v>
+        <v>99212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135601326</v>
       </c>
       <c r="B3" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79468</v>
+        <v>79469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135601328</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135588696</v>
       </c>
       <c r="B7" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135588701</v>
       </c>
       <c r="B8" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>135601327</v>
       </c>
       <c r="B9" t="n">
-        <v>99212</v>
+        <v>99213</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79469</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135588696</v>
       </c>
       <c r="B7" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135588701</v>
       </c>
       <c r="B8" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 27581-2026 artfynd.xlsx
+++ b/artfynd/A 27581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135588699</v>
       </c>
       <c r="B2" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135588705</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135588698</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>135588696</v>
       </c>
       <c r="B7" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135588701</v>
       </c>
       <c r="B8" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>135588707</v>
       </c>
       <c r="B10" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>135588703</v>
       </c>
       <c r="B11" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>135588689</v>
       </c>
       <c r="B12" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>135588682</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>135588683</v>
       </c>
       <c r="B14" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>135588685</v>
       </c>
       <c r="B15" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>135588687</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
